--- a/education_forms/047_learning_equity_accelerator_registration_form--education_forms.xlsx
+++ b/education_forms/047_learning_equity_accelerator_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>organization_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>What is your organization name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>role_in_organization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>What is your role in the organization?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your address?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_state</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your state?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>contact_country</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>What is your country?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_last_name</t>
+          <t>contact_preferences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>What type of information do you want to be contacted with (email, phone, mail)?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_first_name</t>
+          <t>contact_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>What are your comments?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>organization_name</t>
+          <t>contact_city</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Organization Name</t>
+          <t>What is your city?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>role_in_organization</t>
+          <t>contact_zip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Role in Organization</t>
+          <t>What is your zip code?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_address</t>
+          <t>contact_title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>What is your title in the form?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_state</t>
+          <t>contact_terms_conditions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Have you read and agreed to the terms and conditions?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_city</t>
+          <t>contact_further_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>What are your further comments?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_zip</t>
+          <t>contact_privacy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Do you have any comments?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_country</t>
+          <t>contact_agreed_terms</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>What is your agreement status with the terms and conditions?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>contact_privacy</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What type of information do you want to be contacted with?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_terms_conditions</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>By clicking submit, I acknowledge that I have read and agree to the  Terms and Conditions.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>contact_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_comments_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_comments_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contact_comments_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_comments_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_comments_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>contact_comments_7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>contact_comments_8</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1148,80 +918,930 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_country_choices</t>
+          <t>contact_state_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_country_choices</t>
+          <t>contact_state_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_privacy_choices</t>
+          <t>contact_state_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>California</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_privacy_choices</t>
+          <t>contact_state_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>colorado</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>connecticut</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>delaware</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>district_of_columbia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>florida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>georgia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hawaii</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>idaho</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>illinois</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>indiana</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>iowa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>kansas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>kentucky</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>louisiana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>maine</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>maryland</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>massachusetts</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>minnesota</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mississippi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>missouri</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>montana</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nebraska</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nevada</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>new_hampshire</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>new_jersey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>new_mexico</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>new_york</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>north_carolina</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>north_dakota</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ohio</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>oklahoma</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>oregon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pennsylvania</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rhode_island</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>south_carolina</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>south_dakota</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tennessee</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>texas</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>utah</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>vermont</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>virginia</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>washington</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>west_virginia</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wisconsin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>contact_state_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>wyoming</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>contact_country_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>contact_country_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>contact_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>contact_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>contact_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mail</t>
         </is>
       </c>
     </row>
